--- a/tests/SafeOpenXml.Tests/Examples/CellLocking/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/CellLocking/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5131a7a818ff40e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1edb7a6a38c54683"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/CellLocking/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/CellLocking/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1edb7a6a38c54683"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3b869527f5874548"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/CellLocking/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/CellLocking/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3b869527f5874548"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1ebbdfba31ea4b43"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/CellLocking/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/CellLocking/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1ebbdfba31ea4b43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbf6b5271d6674124"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/CellLocking/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/CellLocking/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbf6b5271d6674124"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9da413ea2ee8453f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/CellLocking/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/CellLocking/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9da413ea2ee8453f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R51bdbf67ef074a3b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/CellLocking/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/CellLocking/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R51bdbf67ef074a3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R357f11967f774613"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/CellLocking/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/CellLocking/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R357f11967f774613"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R73d001413cea4c2a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/CellLocking/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/CellLocking/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R73d001413cea4c2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb437e4953c8e4dca"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/CellLocking/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/CellLocking/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb437e4953c8e4dca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7bca618f036a4f77"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/CellLocking/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/CellLocking/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7bca618f036a4f77"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf60aef33eaa34fca"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/CellLocking/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/CellLocking/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf60aef33eaa34fca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R26daf14e93804f4c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/CellLocking/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/CellLocking/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R26daf14e93804f4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Reb29ff49c7c84225"/>
   </x:sheets>
 </x:workbook>
 </file>
